--- a/admin/public/templates/live-class-import-template.xlsx
+++ b/admin/public/templates/live-class-import-template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sessions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lists" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -253,6 +253,16 @@
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Google Meet or In-app. Blank = the default chosen on the import screen.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The LMS module, e.g. "MBT 4 - Order Types &amp; Live Trade" or just "MBT 4". Blank = found from batch + session_number ("MBT" + "4" → MBT 4, "IM" + "4 (1)" → IM 4 - PART 1). Write "none" for no module. The module is what locks a class to the students allowed in it.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Only when the module name alone is not enough. Blank = the course that has the module, else the course chosen on the import screen.</t>
       </text>
     </comment>
   </commentList>
@@ -548,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -589,14 +599,14 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2. In the LMS: Live Classes → Import timetable → upload → choose course, first week, number of weeks.</t>
+          <t>2. In the LMS: Live Classes → Import timetable → upload → choose the course, first week, number of weeks.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3. Check the preview — every class, its dates, mentor and platform. Untick anything you don't want. Nothing is saved yet.</t>
+          <t>3. Check the preview — every class, its module, dates, mentor and platform. Untick anything you don't want. Nothing is saved yet.</t>
         </is>
       </c>
     </row>
@@ -658,7 +668,7 @@
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>• Offline + Online = a room AND an online link. In-app rooms hold at most 30 people by default; use Google Meet for bigger sessions.</t>
+          <t>• Offline + Online = a room AND an online link. In-app rooms hold up to 50 people; use Google Meet for bigger sessions.</t>
         </is>
       </c>
     </row>
@@ -673,6 +683,13 @@
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>• Don't rename the Sessions sheet or its headers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>• Module: each row goes into the LMS module named by batch + session_number ("MBT 4", "IM 4 (1)", "ADVANCE 4") — in the chosen course, or in the academy's other course of the same programme that has it. Or fill the optional module column ("none" = no module). A row whose module is not found is blocked until you pick one in the preview.</t>
         </is>
       </c>
     </row>
@@ -687,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J301"/>
+  <dimension ref="A1:L301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -700,6 +717,8 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,6 +772,16 @@
           <t>platform</t>
         </is>
       </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="n"/>
@@ -765,6 +794,8 @@
       <c r="H2" s="7" t="n"/>
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n"/>
@@ -777,6 +808,8 @@
       <c r="H3" s="7" t="n"/>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -789,6 +822,8 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -801,6 +836,8 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -813,6 +850,8 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -825,6 +864,8 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -837,6 +878,8 @@
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -849,6 +892,8 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -861,6 +906,8 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -873,6 +920,8 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -885,6 +934,8 @@
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -897,6 +948,8 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -909,6 +962,8 @@
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -921,6 +976,8 @@
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -933,6 +990,8 @@
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -945,6 +1004,8 @@
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -957,6 +1018,8 @@
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
       <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -969,6 +1032,8 @@
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -981,6 +1046,8 @@
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -993,6 +1060,8 @@
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -1005,6 +1074,8 @@
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -1017,6 +1088,8 @@
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -1029,6 +1102,8 @@
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -1041,6 +1116,8 @@
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -1053,6 +1130,8 @@
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -1065,6 +1144,8 @@
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -1077,6 +1158,8 @@
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -1089,6 +1172,8 @@
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -1101,6 +1186,8 @@
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -1113,6 +1200,8 @@
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -1125,6 +1214,8 @@
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -1137,6 +1228,8 @@
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -1149,6 +1242,8 @@
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1161,6 +1256,8 @@
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -1173,6 +1270,8 @@
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -1185,6 +1284,8 @@
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -1197,6 +1298,8 @@
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -1209,6 +1312,8 @@
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -1221,6 +1326,8 @@
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="7" t="n"/>
       <c r="J40" s="7" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -1233,6 +1340,8 @@
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -1245,6 +1354,8 @@
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="7" t="n"/>
       <c r="J42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -1257,6 +1368,8 @@
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
       <c r="J43" s="7" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -1269,6 +1382,8 @@
       <c r="H44" s="7" t="n"/>
       <c r="I44" s="7" t="n"/>
       <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -1281,6 +1396,8 @@
       <c r="H45" s="7" t="n"/>
       <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -1293,6 +1410,8 @@
       <c r="H46" s="7" t="n"/>
       <c r="I46" s="7" t="n"/>
       <c r="J46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -1305,6 +1424,8 @@
       <c r="H47" s="7" t="n"/>
       <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -1317,6 +1438,8 @@
       <c r="H48" s="7" t="n"/>
       <c r="I48" s="7" t="n"/>
       <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -1329,6 +1452,8 @@
       <c r="H49" s="7" t="n"/>
       <c r="I49" s="7" t="n"/>
       <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -1341,6 +1466,8 @@
       <c r="H50" s="7" t="n"/>
       <c r="I50" s="7" t="n"/>
       <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -1353,6 +1480,8 @@
       <c r="H51" s="7" t="n"/>
       <c r="I51" s="7" t="n"/>
       <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -1365,6 +1494,8 @@
       <c r="H52" s="7" t="n"/>
       <c r="I52" s="7" t="n"/>
       <c r="J52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -1377,6 +1508,8 @@
       <c r="H53" s="7" t="n"/>
       <c r="I53" s="7" t="n"/>
       <c r="J53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -1389,6 +1522,8 @@
       <c r="H54" s="7" t="n"/>
       <c r="I54" s="7" t="n"/>
       <c r="J54" s="7" t="n"/>
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -1401,6 +1536,8 @@
       <c r="H55" s="7" t="n"/>
       <c r="I55" s="7" t="n"/>
       <c r="J55" s="7" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -1413,6 +1550,8 @@
       <c r="H56" s="7" t="n"/>
       <c r="I56" s="7" t="n"/>
       <c r="J56" s="7" t="n"/>
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -1425,6 +1564,8 @@
       <c r="H57" s="7" t="n"/>
       <c r="I57" s="7" t="n"/>
       <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -1437,6 +1578,8 @@
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
       <c r="J58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -1449,6 +1592,8 @@
       <c r="H59" s="7" t="n"/>
       <c r="I59" s="7" t="n"/>
       <c r="J59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -1461,6 +1606,8 @@
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
       <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -1473,6 +1620,8 @@
       <c r="H61" s="7" t="n"/>
       <c r="I61" s="7" t="n"/>
       <c r="J61" s="7" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -1485,6 +1634,8 @@
       <c r="H62" s="7" t="n"/>
       <c r="I62" s="7" t="n"/>
       <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -1497,6 +1648,8 @@
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
       <c r="J63" s="7" t="n"/>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -1509,6 +1662,8 @@
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n"/>
       <c r="J64" s="7" t="n"/>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -1521,6 +1676,8 @@
       <c r="H65" s="7" t="n"/>
       <c r="I65" s="7" t="n"/>
       <c r="J65" s="7" t="n"/>
+      <c r="K65" s="7" t="n"/>
+      <c r="L65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -1533,6 +1690,8 @@
       <c r="H66" s="7" t="n"/>
       <c r="I66" s="7" t="n"/>
       <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -1545,6 +1704,8 @@
       <c r="H67" s="7" t="n"/>
       <c r="I67" s="7" t="n"/>
       <c r="J67" s="7" t="n"/>
+      <c r="K67" s="7" t="n"/>
+      <c r="L67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -1557,6 +1718,8 @@
       <c r="H68" s="7" t="n"/>
       <c r="I68" s="7" t="n"/>
       <c r="J68" s="7" t="n"/>
+      <c r="K68" s="7" t="n"/>
+      <c r="L68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -1569,6 +1732,8 @@
       <c r="H69" s="7" t="n"/>
       <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -1581,6 +1746,8 @@
       <c r="H70" s="7" t="n"/>
       <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
+      <c r="K70" s="7" t="n"/>
+      <c r="L70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -1593,6 +1760,8 @@
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="n"/>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -1605,6 +1774,8 @@
       <c r="H72" s="7" t="n"/>
       <c r="I72" s="7" t="n"/>
       <c r="J72" s="7" t="n"/>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -1617,6 +1788,8 @@
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -1629,6 +1802,8 @@
       <c r="H74" s="7" t="n"/>
       <c r="I74" s="7" t="n"/>
       <c r="J74" s="7" t="n"/>
+      <c r="K74" s="7" t="n"/>
+      <c r="L74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -1641,6 +1816,8 @@
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="7" t="n"/>
       <c r="J75" s="7" t="n"/>
+      <c r="K75" s="7" t="n"/>
+      <c r="L75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -1653,6 +1830,8 @@
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="n"/>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -1665,6 +1844,8 @@
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="7" t="n"/>
       <c r="J77" s="7" t="n"/>
+      <c r="K77" s="7" t="n"/>
+      <c r="L77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -1677,6 +1858,8 @@
       <c r="H78" s="7" t="n"/>
       <c r="I78" s="7" t="n"/>
       <c r="J78" s="7" t="n"/>
+      <c r="K78" s="7" t="n"/>
+      <c r="L78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -1689,6 +1872,8 @@
       <c r="H79" s="7" t="n"/>
       <c r="I79" s="7" t="n"/>
       <c r="J79" s="7" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -1701,6 +1886,8 @@
       <c r="H80" s="7" t="n"/>
       <c r="I80" s="7" t="n"/>
       <c r="J80" s="7" t="n"/>
+      <c r="K80" s="7" t="n"/>
+      <c r="L80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -1713,6 +1900,8 @@
       <c r="H81" s="7" t="n"/>
       <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
+      <c r="K81" s="7" t="n"/>
+      <c r="L81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -1725,6 +1914,8 @@
       <c r="H82" s="7" t="n"/>
       <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="n"/>
+      <c r="K82" s="7" t="n"/>
+      <c r="L82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -1737,6 +1928,8 @@
       <c r="H83" s="7" t="n"/>
       <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="n"/>
+      <c r="K83" s="7" t="n"/>
+      <c r="L83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -1749,6 +1942,8 @@
       <c r="H84" s="7" t="n"/>
       <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="n"/>
+      <c r="K84" s="7" t="n"/>
+      <c r="L84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -1761,6 +1956,8 @@
       <c r="H85" s="7" t="n"/>
       <c r="I85" s="7" t="n"/>
       <c r="J85" s="7" t="n"/>
+      <c r="K85" s="7" t="n"/>
+      <c r="L85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -1773,6 +1970,8 @@
       <c r="H86" s="7" t="n"/>
       <c r="I86" s="7" t="n"/>
       <c r="J86" s="7" t="n"/>
+      <c r="K86" s="7" t="n"/>
+      <c r="L86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -1785,6 +1984,8 @@
       <c r="H87" s="7" t="n"/>
       <c r="I87" s="7" t="n"/>
       <c r="J87" s="7" t="n"/>
+      <c r="K87" s="7" t="n"/>
+      <c r="L87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -1797,6 +1998,8 @@
       <c r="H88" s="7" t="n"/>
       <c r="I88" s="7" t="n"/>
       <c r="J88" s="7" t="n"/>
+      <c r="K88" s="7" t="n"/>
+      <c r="L88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -1809,6 +2012,8 @@
       <c r="H89" s="7" t="n"/>
       <c r="I89" s="7" t="n"/>
       <c r="J89" s="7" t="n"/>
+      <c r="K89" s="7" t="n"/>
+      <c r="L89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -1821,6 +2026,8 @@
       <c r="H90" s="7" t="n"/>
       <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="n"/>
+      <c r="K90" s="7" t="n"/>
+      <c r="L90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -1833,6 +2040,8 @@
       <c r="H91" s="7" t="n"/>
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="n"/>
+      <c r="K91" s="7" t="n"/>
+      <c r="L91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -1845,6 +2054,8 @@
       <c r="H92" s="7" t="n"/>
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="n"/>
+      <c r="K92" s="7" t="n"/>
+      <c r="L92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -1857,6 +2068,8 @@
       <c r="H93" s="7" t="n"/>
       <c r="I93" s="7" t="n"/>
       <c r="J93" s="7" t="n"/>
+      <c r="K93" s="7" t="n"/>
+      <c r="L93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -1869,6 +2082,8 @@
       <c r="H94" s="7" t="n"/>
       <c r="I94" s="7" t="n"/>
       <c r="J94" s="7" t="n"/>
+      <c r="K94" s="7" t="n"/>
+      <c r="L94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -1881,6 +2096,8 @@
       <c r="H95" s="7" t="n"/>
       <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="n"/>
+      <c r="K95" s="7" t="n"/>
+      <c r="L95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -1893,6 +2110,8 @@
       <c r="H96" s="7" t="n"/>
       <c r="I96" s="7" t="n"/>
       <c r="J96" s="7" t="n"/>
+      <c r="K96" s="7" t="n"/>
+      <c r="L96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -1905,6 +2124,8 @@
       <c r="H97" s="7" t="n"/>
       <c r="I97" s="7" t="n"/>
       <c r="J97" s="7" t="n"/>
+      <c r="K97" s="7" t="n"/>
+      <c r="L97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -1917,6 +2138,8 @@
       <c r="H98" s="7" t="n"/>
       <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="n"/>
+      <c r="K98" s="7" t="n"/>
+      <c r="L98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -1929,6 +2152,8 @@
       <c r="H99" s="7" t="n"/>
       <c r="I99" s="7" t="n"/>
       <c r="J99" s="7" t="n"/>
+      <c r="K99" s="7" t="n"/>
+      <c r="L99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -1941,6 +2166,8 @@
       <c r="H100" s="7" t="n"/>
       <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="n"/>
+      <c r="K100" s="7" t="n"/>
+      <c r="L100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -1953,6 +2180,8 @@
       <c r="H101" s="7" t="n"/>
       <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="n"/>
+      <c r="K101" s="7" t="n"/>
+      <c r="L101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -1965,6 +2194,8 @@
       <c r="H102" s="7" t="n"/>
       <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="n"/>
+      <c r="K102" s="7" t="n"/>
+      <c r="L102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -1977,6 +2208,8 @@
       <c r="H103" s="7" t="n"/>
       <c r="I103" s="7" t="n"/>
       <c r="J103" s="7" t="n"/>
+      <c r="K103" s="7" t="n"/>
+      <c r="L103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -1989,6 +2222,8 @@
       <c r="H104" s="7" t="n"/>
       <c r="I104" s="7" t="n"/>
       <c r="J104" s="7" t="n"/>
+      <c r="K104" s="7" t="n"/>
+      <c r="L104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -2001,6 +2236,8 @@
       <c r="H105" s="7" t="n"/>
       <c r="I105" s="7" t="n"/>
       <c r="J105" s="7" t="n"/>
+      <c r="K105" s="7" t="n"/>
+      <c r="L105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -2013,6 +2250,8 @@
       <c r="H106" s="7" t="n"/>
       <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="n"/>
+      <c r="K106" s="7" t="n"/>
+      <c r="L106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -2025,6 +2264,8 @@
       <c r="H107" s="7" t="n"/>
       <c r="I107" s="7" t="n"/>
       <c r="J107" s="7" t="n"/>
+      <c r="K107" s="7" t="n"/>
+      <c r="L107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -2037,6 +2278,8 @@
       <c r="H108" s="7" t="n"/>
       <c r="I108" s="7" t="n"/>
       <c r="J108" s="7" t="n"/>
+      <c r="K108" s="7" t="n"/>
+      <c r="L108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -2049,6 +2292,8 @@
       <c r="H109" s="7" t="n"/>
       <c r="I109" s="7" t="n"/>
       <c r="J109" s="7" t="n"/>
+      <c r="K109" s="7" t="n"/>
+      <c r="L109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -2061,6 +2306,8 @@
       <c r="H110" s="7" t="n"/>
       <c r="I110" s="7" t="n"/>
       <c r="J110" s="7" t="n"/>
+      <c r="K110" s="7" t="n"/>
+      <c r="L110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -2073,6 +2320,8 @@
       <c r="H111" s="7" t="n"/>
       <c r="I111" s="7" t="n"/>
       <c r="J111" s="7" t="n"/>
+      <c r="K111" s="7" t="n"/>
+      <c r="L111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -2085,6 +2334,8 @@
       <c r="H112" s="7" t="n"/>
       <c r="I112" s="7" t="n"/>
       <c r="J112" s="7" t="n"/>
+      <c r="K112" s="7" t="n"/>
+      <c r="L112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -2097,6 +2348,8 @@
       <c r="H113" s="7" t="n"/>
       <c r="I113" s="7" t="n"/>
       <c r="J113" s="7" t="n"/>
+      <c r="K113" s="7" t="n"/>
+      <c r="L113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -2109,6 +2362,8 @@
       <c r="H114" s="7" t="n"/>
       <c r="I114" s="7" t="n"/>
       <c r="J114" s="7" t="n"/>
+      <c r="K114" s="7" t="n"/>
+      <c r="L114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -2121,6 +2376,8 @@
       <c r="H115" s="7" t="n"/>
       <c r="I115" s="7" t="n"/>
       <c r="J115" s="7" t="n"/>
+      <c r="K115" s="7" t="n"/>
+      <c r="L115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -2133,6 +2390,8 @@
       <c r="H116" s="7" t="n"/>
       <c r="I116" s="7" t="n"/>
       <c r="J116" s="7" t="n"/>
+      <c r="K116" s="7" t="n"/>
+      <c r="L116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -2145,6 +2404,8 @@
       <c r="H117" s="7" t="n"/>
       <c r="I117" s="7" t="n"/>
       <c r="J117" s="7" t="n"/>
+      <c r="K117" s="7" t="n"/>
+      <c r="L117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -2157,6 +2418,8 @@
       <c r="H118" s="7" t="n"/>
       <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
+      <c r="K118" s="7" t="n"/>
+      <c r="L118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -2169,6 +2432,8 @@
       <c r="H119" s="7" t="n"/>
       <c r="I119" s="7" t="n"/>
       <c r="J119" s="7" t="n"/>
+      <c r="K119" s="7" t="n"/>
+      <c r="L119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -2181,6 +2446,8 @@
       <c r="H120" s="7" t="n"/>
       <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="n"/>
+      <c r="K120" s="7" t="n"/>
+      <c r="L120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -2193,6 +2460,8 @@
       <c r="H121" s="7" t="n"/>
       <c r="I121" s="7" t="n"/>
       <c r="J121" s="7" t="n"/>
+      <c r="K121" s="7" t="n"/>
+      <c r="L121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -2205,6 +2474,8 @@
       <c r="H122" s="7" t="n"/>
       <c r="I122" s="7" t="n"/>
       <c r="J122" s="7" t="n"/>
+      <c r="K122" s="7" t="n"/>
+      <c r="L122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -2217,6 +2488,8 @@
       <c r="H123" s="7" t="n"/>
       <c r="I123" s="7" t="n"/>
       <c r="J123" s="7" t="n"/>
+      <c r="K123" s="7" t="n"/>
+      <c r="L123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -2229,6 +2502,8 @@
       <c r="H124" s="7" t="n"/>
       <c r="I124" s="7" t="n"/>
       <c r="J124" s="7" t="n"/>
+      <c r="K124" s="7" t="n"/>
+      <c r="L124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -2241,6 +2516,8 @@
       <c r="H125" s="7" t="n"/>
       <c r="I125" s="7" t="n"/>
       <c r="J125" s="7" t="n"/>
+      <c r="K125" s="7" t="n"/>
+      <c r="L125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -2253,6 +2530,8 @@
       <c r="H126" s="7" t="n"/>
       <c r="I126" s="7" t="n"/>
       <c r="J126" s="7" t="n"/>
+      <c r="K126" s="7" t="n"/>
+      <c r="L126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -2265,6 +2544,8 @@
       <c r="H127" s="7" t="n"/>
       <c r="I127" s="7" t="n"/>
       <c r="J127" s="7" t="n"/>
+      <c r="K127" s="7" t="n"/>
+      <c r="L127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -2277,6 +2558,8 @@
       <c r="H128" s="7" t="n"/>
       <c r="I128" s="7" t="n"/>
       <c r="J128" s="7" t="n"/>
+      <c r="K128" s="7" t="n"/>
+      <c r="L128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -2289,6 +2572,8 @@
       <c r="H129" s="7" t="n"/>
       <c r="I129" s="7" t="n"/>
       <c r="J129" s="7" t="n"/>
+      <c r="K129" s="7" t="n"/>
+      <c r="L129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -2301,6 +2586,8 @@
       <c r="H130" s="7" t="n"/>
       <c r="I130" s="7" t="n"/>
       <c r="J130" s="7" t="n"/>
+      <c r="K130" s="7" t="n"/>
+      <c r="L130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -2313,6 +2600,8 @@
       <c r="H131" s="7" t="n"/>
       <c r="I131" s="7" t="n"/>
       <c r="J131" s="7" t="n"/>
+      <c r="K131" s="7" t="n"/>
+      <c r="L131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -2325,6 +2614,8 @@
       <c r="H132" s="7" t="n"/>
       <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
+      <c r="K132" s="7" t="n"/>
+      <c r="L132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -2337,6 +2628,8 @@
       <c r="H133" s="7" t="n"/>
       <c r="I133" s="7" t="n"/>
       <c r="J133" s="7" t="n"/>
+      <c r="K133" s="7" t="n"/>
+      <c r="L133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -2349,6 +2642,8 @@
       <c r="H134" s="7" t="n"/>
       <c r="I134" s="7" t="n"/>
       <c r="J134" s="7" t="n"/>
+      <c r="K134" s="7" t="n"/>
+      <c r="L134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -2361,6 +2656,8 @@
       <c r="H135" s="7" t="n"/>
       <c r="I135" s="7" t="n"/>
       <c r="J135" s="7" t="n"/>
+      <c r="K135" s="7" t="n"/>
+      <c r="L135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -2373,6 +2670,8 @@
       <c r="H136" s="7" t="n"/>
       <c r="I136" s="7" t="n"/>
       <c r="J136" s="7" t="n"/>
+      <c r="K136" s="7" t="n"/>
+      <c r="L136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -2385,6 +2684,8 @@
       <c r="H137" s="7" t="n"/>
       <c r="I137" s="7" t="n"/>
       <c r="J137" s="7" t="n"/>
+      <c r="K137" s="7" t="n"/>
+      <c r="L137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -2397,6 +2698,8 @@
       <c r="H138" s="7" t="n"/>
       <c r="I138" s="7" t="n"/>
       <c r="J138" s="7" t="n"/>
+      <c r="K138" s="7" t="n"/>
+      <c r="L138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -2409,6 +2712,8 @@
       <c r="H139" s="7" t="n"/>
       <c r="I139" s="7" t="n"/>
       <c r="J139" s="7" t="n"/>
+      <c r="K139" s="7" t="n"/>
+      <c r="L139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -2421,6 +2726,8 @@
       <c r="H140" s="7" t="n"/>
       <c r="I140" s="7" t="n"/>
       <c r="J140" s="7" t="n"/>
+      <c r="K140" s="7" t="n"/>
+      <c r="L140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -2433,6 +2740,8 @@
       <c r="H141" s="7" t="n"/>
       <c r="I141" s="7" t="n"/>
       <c r="J141" s="7" t="n"/>
+      <c r="K141" s="7" t="n"/>
+      <c r="L141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -2445,6 +2754,8 @@
       <c r="H142" s="7" t="n"/>
       <c r="I142" s="7" t="n"/>
       <c r="J142" s="7" t="n"/>
+      <c r="K142" s="7" t="n"/>
+      <c r="L142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -2457,6 +2768,8 @@
       <c r="H143" s="7" t="n"/>
       <c r="I143" s="7" t="n"/>
       <c r="J143" s="7" t="n"/>
+      <c r="K143" s="7" t="n"/>
+      <c r="L143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -2469,6 +2782,8 @@
       <c r="H144" s="7" t="n"/>
       <c r="I144" s="7" t="n"/>
       <c r="J144" s="7" t="n"/>
+      <c r="K144" s="7" t="n"/>
+      <c r="L144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -2481,6 +2796,8 @@
       <c r="H145" s="7" t="n"/>
       <c r="I145" s="7" t="n"/>
       <c r="J145" s="7" t="n"/>
+      <c r="K145" s="7" t="n"/>
+      <c r="L145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -2493,6 +2810,8 @@
       <c r="H146" s="7" t="n"/>
       <c r="I146" s="7" t="n"/>
       <c r="J146" s="7" t="n"/>
+      <c r="K146" s="7" t="n"/>
+      <c r="L146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -2505,6 +2824,8 @@
       <c r="H147" s="7" t="n"/>
       <c r="I147" s="7" t="n"/>
       <c r="J147" s="7" t="n"/>
+      <c r="K147" s="7" t="n"/>
+      <c r="L147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -2517,6 +2838,8 @@
       <c r="H148" s="7" t="n"/>
       <c r="I148" s="7" t="n"/>
       <c r="J148" s="7" t="n"/>
+      <c r="K148" s="7" t="n"/>
+      <c r="L148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -2529,6 +2852,8 @@
       <c r="H149" s="7" t="n"/>
       <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
+      <c r="K149" s="7" t="n"/>
+      <c r="L149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -2541,6 +2866,8 @@
       <c r="H150" s="7" t="n"/>
       <c r="I150" s="7" t="n"/>
       <c r="J150" s="7" t="n"/>
+      <c r="K150" s="7" t="n"/>
+      <c r="L150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -2553,6 +2880,8 @@
       <c r="H151" s="7" t="n"/>
       <c r="I151" s="7" t="n"/>
       <c r="J151" s="7" t="n"/>
+      <c r="K151" s="7" t="n"/>
+      <c r="L151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -2565,6 +2894,8 @@
       <c r="H152" s="7" t="n"/>
       <c r="I152" s="7" t="n"/>
       <c r="J152" s="7" t="n"/>
+      <c r="K152" s="7" t="n"/>
+      <c r="L152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -2577,6 +2908,8 @@
       <c r="H153" s="7" t="n"/>
       <c r="I153" s="7" t="n"/>
       <c r="J153" s="7" t="n"/>
+      <c r="K153" s="7" t="n"/>
+      <c r="L153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -2589,6 +2922,8 @@
       <c r="H154" s="7" t="n"/>
       <c r="I154" s="7" t="n"/>
       <c r="J154" s="7" t="n"/>
+      <c r="K154" s="7" t="n"/>
+      <c r="L154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -2601,6 +2936,8 @@
       <c r="H155" s="7" t="n"/>
       <c r="I155" s="7" t="n"/>
       <c r="J155" s="7" t="n"/>
+      <c r="K155" s="7" t="n"/>
+      <c r="L155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -2613,6 +2950,8 @@
       <c r="H156" s="7" t="n"/>
       <c r="I156" s="7" t="n"/>
       <c r="J156" s="7" t="n"/>
+      <c r="K156" s="7" t="n"/>
+      <c r="L156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -2625,6 +2964,8 @@
       <c r="H157" s="7" t="n"/>
       <c r="I157" s="7" t="n"/>
       <c r="J157" s="7" t="n"/>
+      <c r="K157" s="7" t="n"/>
+      <c r="L157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -2637,6 +2978,8 @@
       <c r="H158" s="7" t="n"/>
       <c r="I158" s="7" t="n"/>
       <c r="J158" s="7" t="n"/>
+      <c r="K158" s="7" t="n"/>
+      <c r="L158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -2649,6 +2992,8 @@
       <c r="H159" s="7" t="n"/>
       <c r="I159" s="7" t="n"/>
       <c r="J159" s="7" t="n"/>
+      <c r="K159" s="7" t="n"/>
+      <c r="L159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -2661,6 +3006,8 @@
       <c r="H160" s="7" t="n"/>
       <c r="I160" s="7" t="n"/>
       <c r="J160" s="7" t="n"/>
+      <c r="K160" s="7" t="n"/>
+      <c r="L160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -2673,6 +3020,8 @@
       <c r="H161" s="7" t="n"/>
       <c r="I161" s="7" t="n"/>
       <c r="J161" s="7" t="n"/>
+      <c r="K161" s="7" t="n"/>
+      <c r="L161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -2685,6 +3034,8 @@
       <c r="H162" s="7" t="n"/>
       <c r="I162" s="7" t="n"/>
       <c r="J162" s="7" t="n"/>
+      <c r="K162" s="7" t="n"/>
+      <c r="L162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -2697,6 +3048,8 @@
       <c r="H163" s="7" t="n"/>
       <c r="I163" s="7" t="n"/>
       <c r="J163" s="7" t="n"/>
+      <c r="K163" s="7" t="n"/>
+      <c r="L163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -2709,6 +3062,8 @@
       <c r="H164" s="7" t="n"/>
       <c r="I164" s="7" t="n"/>
       <c r="J164" s="7" t="n"/>
+      <c r="K164" s="7" t="n"/>
+      <c r="L164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -2721,6 +3076,8 @@
       <c r="H165" s="7" t="n"/>
       <c r="I165" s="7" t="n"/>
       <c r="J165" s="7" t="n"/>
+      <c r="K165" s="7" t="n"/>
+      <c r="L165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -2733,6 +3090,8 @@
       <c r="H166" s="7" t="n"/>
       <c r="I166" s="7" t="n"/>
       <c r="J166" s="7" t="n"/>
+      <c r="K166" s="7" t="n"/>
+      <c r="L166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -2745,6 +3104,8 @@
       <c r="H167" s="7" t="n"/>
       <c r="I167" s="7" t="n"/>
       <c r="J167" s="7" t="n"/>
+      <c r="K167" s="7" t="n"/>
+      <c r="L167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -2757,6 +3118,8 @@
       <c r="H168" s="7" t="n"/>
       <c r="I168" s="7" t="n"/>
       <c r="J168" s="7" t="n"/>
+      <c r="K168" s="7" t="n"/>
+      <c r="L168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -2769,6 +3132,8 @@
       <c r="H169" s="7" t="n"/>
       <c r="I169" s="7" t="n"/>
       <c r="J169" s="7" t="n"/>
+      <c r="K169" s="7" t="n"/>
+      <c r="L169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -2781,6 +3146,8 @@
       <c r="H170" s="7" t="n"/>
       <c r="I170" s="7" t="n"/>
       <c r="J170" s="7" t="n"/>
+      <c r="K170" s="7" t="n"/>
+      <c r="L170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -2793,6 +3160,8 @@
       <c r="H171" s="7" t="n"/>
       <c r="I171" s="7" t="n"/>
       <c r="J171" s="7" t="n"/>
+      <c r="K171" s="7" t="n"/>
+      <c r="L171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -2805,6 +3174,8 @@
       <c r="H172" s="7" t="n"/>
       <c r="I172" s="7" t="n"/>
       <c r="J172" s="7" t="n"/>
+      <c r="K172" s="7" t="n"/>
+      <c r="L172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -2817,6 +3188,8 @@
       <c r="H173" s="7" t="n"/>
       <c r="I173" s="7" t="n"/>
       <c r="J173" s="7" t="n"/>
+      <c r="K173" s="7" t="n"/>
+      <c r="L173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -2829,6 +3202,8 @@
       <c r="H174" s="7" t="n"/>
       <c r="I174" s="7" t="n"/>
       <c r="J174" s="7" t="n"/>
+      <c r="K174" s="7" t="n"/>
+      <c r="L174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -2841,6 +3216,8 @@
       <c r="H175" s="7" t="n"/>
       <c r="I175" s="7" t="n"/>
       <c r="J175" s="7" t="n"/>
+      <c r="K175" s="7" t="n"/>
+      <c r="L175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -2853,6 +3230,8 @@
       <c r="H176" s="7" t="n"/>
       <c r="I176" s="7" t="n"/>
       <c r="J176" s="7" t="n"/>
+      <c r="K176" s="7" t="n"/>
+      <c r="L176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -2865,6 +3244,8 @@
       <c r="H177" s="7" t="n"/>
       <c r="I177" s="7" t="n"/>
       <c r="J177" s="7" t="n"/>
+      <c r="K177" s="7" t="n"/>
+      <c r="L177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -2877,6 +3258,8 @@
       <c r="H178" s="7" t="n"/>
       <c r="I178" s="7" t="n"/>
       <c r="J178" s="7" t="n"/>
+      <c r="K178" s="7" t="n"/>
+      <c r="L178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -2889,6 +3272,8 @@
       <c r="H179" s="7" t="n"/>
       <c r="I179" s="7" t="n"/>
       <c r="J179" s="7" t="n"/>
+      <c r="K179" s="7" t="n"/>
+      <c r="L179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -2901,6 +3286,8 @@
       <c r="H180" s="7" t="n"/>
       <c r="I180" s="7" t="n"/>
       <c r="J180" s="7" t="n"/>
+      <c r="K180" s="7" t="n"/>
+      <c r="L180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -2913,6 +3300,8 @@
       <c r="H181" s="7" t="n"/>
       <c r="I181" s="7" t="n"/>
       <c r="J181" s="7" t="n"/>
+      <c r="K181" s="7" t="n"/>
+      <c r="L181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -2925,6 +3314,8 @@
       <c r="H182" s="7" t="n"/>
       <c r="I182" s="7" t="n"/>
       <c r="J182" s="7" t="n"/>
+      <c r="K182" s="7" t="n"/>
+      <c r="L182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -2937,6 +3328,8 @@
       <c r="H183" s="7" t="n"/>
       <c r="I183" s="7" t="n"/>
       <c r="J183" s="7" t="n"/>
+      <c r="K183" s="7" t="n"/>
+      <c r="L183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -2949,6 +3342,8 @@
       <c r="H184" s="7" t="n"/>
       <c r="I184" s="7" t="n"/>
       <c r="J184" s="7" t="n"/>
+      <c r="K184" s="7" t="n"/>
+      <c r="L184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -2961,6 +3356,8 @@
       <c r="H185" s="7" t="n"/>
       <c r="I185" s="7" t="n"/>
       <c r="J185" s="7" t="n"/>
+      <c r="K185" s="7" t="n"/>
+      <c r="L185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -2973,6 +3370,8 @@
       <c r="H186" s="7" t="n"/>
       <c r="I186" s="7" t="n"/>
       <c r="J186" s="7" t="n"/>
+      <c r="K186" s="7" t="n"/>
+      <c r="L186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -2985,6 +3384,8 @@
       <c r="H187" s="7" t="n"/>
       <c r="I187" s="7" t="n"/>
       <c r="J187" s="7" t="n"/>
+      <c r="K187" s="7" t="n"/>
+      <c r="L187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -2997,6 +3398,8 @@
       <c r="H188" s="7" t="n"/>
       <c r="I188" s="7" t="n"/>
       <c r="J188" s="7" t="n"/>
+      <c r="K188" s="7" t="n"/>
+      <c r="L188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -3009,6 +3412,8 @@
       <c r="H189" s="7" t="n"/>
       <c r="I189" s="7" t="n"/>
       <c r="J189" s="7" t="n"/>
+      <c r="K189" s="7" t="n"/>
+      <c r="L189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -3021,6 +3426,8 @@
       <c r="H190" s="7" t="n"/>
       <c r="I190" s="7" t="n"/>
       <c r="J190" s="7" t="n"/>
+      <c r="K190" s="7" t="n"/>
+      <c r="L190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -3033,6 +3440,8 @@
       <c r="H191" s="7" t="n"/>
       <c r="I191" s="7" t="n"/>
       <c r="J191" s="7" t="n"/>
+      <c r="K191" s="7" t="n"/>
+      <c r="L191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -3045,6 +3454,8 @@
       <c r="H192" s="7" t="n"/>
       <c r="I192" s="7" t="n"/>
       <c r="J192" s="7" t="n"/>
+      <c r="K192" s="7" t="n"/>
+      <c r="L192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -3057,6 +3468,8 @@
       <c r="H193" s="7" t="n"/>
       <c r="I193" s="7" t="n"/>
       <c r="J193" s="7" t="n"/>
+      <c r="K193" s="7" t="n"/>
+      <c r="L193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -3069,6 +3482,8 @@
       <c r="H194" s="7" t="n"/>
       <c r="I194" s="7" t="n"/>
       <c r="J194" s="7" t="n"/>
+      <c r="K194" s="7" t="n"/>
+      <c r="L194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -3081,6 +3496,8 @@
       <c r="H195" s="7" t="n"/>
       <c r="I195" s="7" t="n"/>
       <c r="J195" s="7" t="n"/>
+      <c r="K195" s="7" t="n"/>
+      <c r="L195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -3093,6 +3510,8 @@
       <c r="H196" s="7" t="n"/>
       <c r="I196" s="7" t="n"/>
       <c r="J196" s="7" t="n"/>
+      <c r="K196" s="7" t="n"/>
+      <c r="L196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -3105,6 +3524,8 @@
       <c r="H197" s="7" t="n"/>
       <c r="I197" s="7" t="n"/>
       <c r="J197" s="7" t="n"/>
+      <c r="K197" s="7" t="n"/>
+      <c r="L197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -3117,6 +3538,8 @@
       <c r="H198" s="7" t="n"/>
       <c r="I198" s="7" t="n"/>
       <c r="J198" s="7" t="n"/>
+      <c r="K198" s="7" t="n"/>
+      <c r="L198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -3129,6 +3552,8 @@
       <c r="H199" s="7" t="n"/>
       <c r="I199" s="7" t="n"/>
       <c r="J199" s="7" t="n"/>
+      <c r="K199" s="7" t="n"/>
+      <c r="L199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -3141,6 +3566,8 @@
       <c r="H200" s="7" t="n"/>
       <c r="I200" s="7" t="n"/>
       <c r="J200" s="7" t="n"/>
+      <c r="K200" s="7" t="n"/>
+      <c r="L200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -3153,6 +3580,8 @@
       <c r="H201" s="7" t="n"/>
       <c r="I201" s="7" t="n"/>
       <c r="J201" s="7" t="n"/>
+      <c r="K201" s="7" t="n"/>
+      <c r="L201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -3165,6 +3594,8 @@
       <c r="H202" s="7" t="n"/>
       <c r="I202" s="7" t="n"/>
       <c r="J202" s="7" t="n"/>
+      <c r="K202" s="7" t="n"/>
+      <c r="L202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -3177,6 +3608,8 @@
       <c r="H203" s="7" t="n"/>
       <c r="I203" s="7" t="n"/>
       <c r="J203" s="7" t="n"/>
+      <c r="K203" s="7" t="n"/>
+      <c r="L203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -3189,6 +3622,8 @@
       <c r="H204" s="7" t="n"/>
       <c r="I204" s="7" t="n"/>
       <c r="J204" s="7" t="n"/>
+      <c r="K204" s="7" t="n"/>
+      <c r="L204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -3201,6 +3636,8 @@
       <c r="H205" s="7" t="n"/>
       <c r="I205" s="7" t="n"/>
       <c r="J205" s="7" t="n"/>
+      <c r="K205" s="7" t="n"/>
+      <c r="L205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -3213,6 +3650,8 @@
       <c r="H206" s="7" t="n"/>
       <c r="I206" s="7" t="n"/>
       <c r="J206" s="7" t="n"/>
+      <c r="K206" s="7" t="n"/>
+      <c r="L206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -3225,6 +3664,8 @@
       <c r="H207" s="7" t="n"/>
       <c r="I207" s="7" t="n"/>
       <c r="J207" s="7" t="n"/>
+      <c r="K207" s="7" t="n"/>
+      <c r="L207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -3237,6 +3678,8 @@
       <c r="H208" s="7" t="n"/>
       <c r="I208" s="7" t="n"/>
       <c r="J208" s="7" t="n"/>
+      <c r="K208" s="7" t="n"/>
+      <c r="L208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -3249,6 +3692,8 @@
       <c r="H209" s="7" t="n"/>
       <c r="I209" s="7" t="n"/>
       <c r="J209" s="7" t="n"/>
+      <c r="K209" s="7" t="n"/>
+      <c r="L209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -3261,6 +3706,8 @@
       <c r="H210" s="7" t="n"/>
       <c r="I210" s="7" t="n"/>
       <c r="J210" s="7" t="n"/>
+      <c r="K210" s="7" t="n"/>
+      <c r="L210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -3273,6 +3720,8 @@
       <c r="H211" s="7" t="n"/>
       <c r="I211" s="7" t="n"/>
       <c r="J211" s="7" t="n"/>
+      <c r="K211" s="7" t="n"/>
+      <c r="L211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -3285,6 +3734,8 @@
       <c r="H212" s="7" t="n"/>
       <c r="I212" s="7" t="n"/>
       <c r="J212" s="7" t="n"/>
+      <c r="K212" s="7" t="n"/>
+      <c r="L212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -3297,6 +3748,8 @@
       <c r="H213" s="7" t="n"/>
       <c r="I213" s="7" t="n"/>
       <c r="J213" s="7" t="n"/>
+      <c r="K213" s="7" t="n"/>
+      <c r="L213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -3309,6 +3762,8 @@
       <c r="H214" s="7" t="n"/>
       <c r="I214" s="7" t="n"/>
       <c r="J214" s="7" t="n"/>
+      <c r="K214" s="7" t="n"/>
+      <c r="L214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -3321,6 +3776,8 @@
       <c r="H215" s="7" t="n"/>
       <c r="I215" s="7" t="n"/>
       <c r="J215" s="7" t="n"/>
+      <c r="K215" s="7" t="n"/>
+      <c r="L215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -3333,6 +3790,8 @@
       <c r="H216" s="7" t="n"/>
       <c r="I216" s="7" t="n"/>
       <c r="J216" s="7" t="n"/>
+      <c r="K216" s="7" t="n"/>
+      <c r="L216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -3345,6 +3804,8 @@
       <c r="H217" s="7" t="n"/>
       <c r="I217" s="7" t="n"/>
       <c r="J217" s="7" t="n"/>
+      <c r="K217" s="7" t="n"/>
+      <c r="L217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -3357,6 +3818,8 @@
       <c r="H218" s="7" t="n"/>
       <c r="I218" s="7" t="n"/>
       <c r="J218" s="7" t="n"/>
+      <c r="K218" s="7" t="n"/>
+      <c r="L218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -3369,6 +3832,8 @@
       <c r="H219" s="7" t="n"/>
       <c r="I219" s="7" t="n"/>
       <c r="J219" s="7" t="n"/>
+      <c r="K219" s="7" t="n"/>
+      <c r="L219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -3381,6 +3846,8 @@
       <c r="H220" s="7" t="n"/>
       <c r="I220" s="7" t="n"/>
       <c r="J220" s="7" t="n"/>
+      <c r="K220" s="7" t="n"/>
+      <c r="L220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -3393,6 +3860,8 @@
       <c r="H221" s="7" t="n"/>
       <c r="I221" s="7" t="n"/>
       <c r="J221" s="7" t="n"/>
+      <c r="K221" s="7" t="n"/>
+      <c r="L221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -3405,6 +3874,8 @@
       <c r="H222" s="7" t="n"/>
       <c r="I222" s="7" t="n"/>
       <c r="J222" s="7" t="n"/>
+      <c r="K222" s="7" t="n"/>
+      <c r="L222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -3417,6 +3888,8 @@
       <c r="H223" s="7" t="n"/>
       <c r="I223" s="7" t="n"/>
       <c r="J223" s="7" t="n"/>
+      <c r="K223" s="7" t="n"/>
+      <c r="L223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -3429,6 +3902,8 @@
       <c r="H224" s="7" t="n"/>
       <c r="I224" s="7" t="n"/>
       <c r="J224" s="7" t="n"/>
+      <c r="K224" s="7" t="n"/>
+      <c r="L224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -3441,6 +3916,8 @@
       <c r="H225" s="7" t="n"/>
       <c r="I225" s="7" t="n"/>
       <c r="J225" s="7" t="n"/>
+      <c r="K225" s="7" t="n"/>
+      <c r="L225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -3453,6 +3930,8 @@
       <c r="H226" s="7" t="n"/>
       <c r="I226" s="7" t="n"/>
       <c r="J226" s="7" t="n"/>
+      <c r="K226" s="7" t="n"/>
+      <c r="L226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -3465,6 +3944,8 @@
       <c r="H227" s="7" t="n"/>
       <c r="I227" s="7" t="n"/>
       <c r="J227" s="7" t="n"/>
+      <c r="K227" s="7" t="n"/>
+      <c r="L227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -3477,6 +3958,8 @@
       <c r="H228" s="7" t="n"/>
       <c r="I228" s="7" t="n"/>
       <c r="J228" s="7" t="n"/>
+      <c r="K228" s="7" t="n"/>
+      <c r="L228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -3489,6 +3972,8 @@
       <c r="H229" s="7" t="n"/>
       <c r="I229" s="7" t="n"/>
       <c r="J229" s="7" t="n"/>
+      <c r="K229" s="7" t="n"/>
+      <c r="L229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -3501,6 +3986,8 @@
       <c r="H230" s="7" t="n"/>
       <c r="I230" s="7" t="n"/>
       <c r="J230" s="7" t="n"/>
+      <c r="K230" s="7" t="n"/>
+      <c r="L230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -3513,6 +4000,8 @@
       <c r="H231" s="7" t="n"/>
       <c r="I231" s="7" t="n"/>
       <c r="J231" s="7" t="n"/>
+      <c r="K231" s="7" t="n"/>
+      <c r="L231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -3525,6 +4014,8 @@
       <c r="H232" s="7" t="n"/>
       <c r="I232" s="7" t="n"/>
       <c r="J232" s="7" t="n"/>
+      <c r="K232" s="7" t="n"/>
+      <c r="L232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -3537,6 +4028,8 @@
       <c r="H233" s="7" t="n"/>
       <c r="I233" s="7" t="n"/>
       <c r="J233" s="7" t="n"/>
+      <c r="K233" s="7" t="n"/>
+      <c r="L233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -3549,6 +4042,8 @@
       <c r="H234" s="7" t="n"/>
       <c r="I234" s="7" t="n"/>
       <c r="J234" s="7" t="n"/>
+      <c r="K234" s="7" t="n"/>
+      <c r="L234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -3561,6 +4056,8 @@
       <c r="H235" s="7" t="n"/>
       <c r="I235" s="7" t="n"/>
       <c r="J235" s="7" t="n"/>
+      <c r="K235" s="7" t="n"/>
+      <c r="L235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -3573,6 +4070,8 @@
       <c r="H236" s="7" t="n"/>
       <c r="I236" s="7" t="n"/>
       <c r="J236" s="7" t="n"/>
+      <c r="K236" s="7" t="n"/>
+      <c r="L236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -3585,6 +4084,8 @@
       <c r="H237" s="7" t="n"/>
       <c r="I237" s="7" t="n"/>
       <c r="J237" s="7" t="n"/>
+      <c r="K237" s="7" t="n"/>
+      <c r="L237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -3597,6 +4098,8 @@
       <c r="H238" s="7" t="n"/>
       <c r="I238" s="7" t="n"/>
       <c r="J238" s="7" t="n"/>
+      <c r="K238" s="7" t="n"/>
+      <c r="L238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -3609,6 +4112,8 @@
       <c r="H239" s="7" t="n"/>
       <c r="I239" s="7" t="n"/>
       <c r="J239" s="7" t="n"/>
+      <c r="K239" s="7" t="n"/>
+      <c r="L239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -3621,6 +4126,8 @@
       <c r="H240" s="7" t="n"/>
       <c r="I240" s="7" t="n"/>
       <c r="J240" s="7" t="n"/>
+      <c r="K240" s="7" t="n"/>
+      <c r="L240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -3633,6 +4140,8 @@
       <c r="H241" s="7" t="n"/>
       <c r="I241" s="7" t="n"/>
       <c r="J241" s="7" t="n"/>
+      <c r="K241" s="7" t="n"/>
+      <c r="L241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -3645,6 +4154,8 @@
       <c r="H242" s="7" t="n"/>
       <c r="I242" s="7" t="n"/>
       <c r="J242" s="7" t="n"/>
+      <c r="K242" s="7" t="n"/>
+      <c r="L242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -3657,6 +4168,8 @@
       <c r="H243" s="7" t="n"/>
       <c r="I243" s="7" t="n"/>
       <c r="J243" s="7" t="n"/>
+      <c r="K243" s="7" t="n"/>
+      <c r="L243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -3669,6 +4182,8 @@
       <c r="H244" s="7" t="n"/>
       <c r="I244" s="7" t="n"/>
       <c r="J244" s="7" t="n"/>
+      <c r="K244" s="7" t="n"/>
+      <c r="L244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -3681,6 +4196,8 @@
       <c r="H245" s="7" t="n"/>
       <c r="I245" s="7" t="n"/>
       <c r="J245" s="7" t="n"/>
+      <c r="K245" s="7" t="n"/>
+      <c r="L245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -3693,6 +4210,8 @@
       <c r="H246" s="7" t="n"/>
       <c r="I246" s="7" t="n"/>
       <c r="J246" s="7" t="n"/>
+      <c r="K246" s="7" t="n"/>
+      <c r="L246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -3705,6 +4224,8 @@
       <c r="H247" s="7" t="n"/>
       <c r="I247" s="7" t="n"/>
       <c r="J247" s="7" t="n"/>
+      <c r="K247" s="7" t="n"/>
+      <c r="L247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -3717,6 +4238,8 @@
       <c r="H248" s="7" t="n"/>
       <c r="I248" s="7" t="n"/>
       <c r="J248" s="7" t="n"/>
+      <c r="K248" s="7" t="n"/>
+      <c r="L248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -3729,6 +4252,8 @@
       <c r="H249" s="7" t="n"/>
       <c r="I249" s="7" t="n"/>
       <c r="J249" s="7" t="n"/>
+      <c r="K249" s="7" t="n"/>
+      <c r="L249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -3741,6 +4266,8 @@
       <c r="H250" s="7" t="n"/>
       <c r="I250" s="7" t="n"/>
       <c r="J250" s="7" t="n"/>
+      <c r="K250" s="7" t="n"/>
+      <c r="L250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -3753,6 +4280,8 @@
       <c r="H251" s="7" t="n"/>
       <c r="I251" s="7" t="n"/>
       <c r="J251" s="7" t="n"/>
+      <c r="K251" s="7" t="n"/>
+      <c r="L251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -3765,6 +4294,8 @@
       <c r="H252" s="7" t="n"/>
       <c r="I252" s="7" t="n"/>
       <c r="J252" s="7" t="n"/>
+      <c r="K252" s="7" t="n"/>
+      <c r="L252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n"/>
@@ -3777,6 +4308,8 @@
       <c r="H253" s="7" t="n"/>
       <c r="I253" s="7" t="n"/>
       <c r="J253" s="7" t="n"/>
+      <c r="K253" s="7" t="n"/>
+      <c r="L253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="7" t="n"/>
@@ -3789,6 +4322,8 @@
       <c r="H254" s="7" t="n"/>
       <c r="I254" s="7" t="n"/>
       <c r="J254" s="7" t="n"/>
+      <c r="K254" s="7" t="n"/>
+      <c r="L254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="7" t="n"/>
@@ -3801,6 +4336,8 @@
       <c r="H255" s="7" t="n"/>
       <c r="I255" s="7" t="n"/>
       <c r="J255" s="7" t="n"/>
+      <c r="K255" s="7" t="n"/>
+      <c r="L255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -3813,6 +4350,8 @@
       <c r="H256" s="7" t="n"/>
       <c r="I256" s="7" t="n"/>
       <c r="J256" s="7" t="n"/>
+      <c r="K256" s="7" t="n"/>
+      <c r="L256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -3825,6 +4364,8 @@
       <c r="H257" s="7" t="n"/>
       <c r="I257" s="7" t="n"/>
       <c r="J257" s="7" t="n"/>
+      <c r="K257" s="7" t="n"/>
+      <c r="L257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -3837,6 +4378,8 @@
       <c r="H258" s="7" t="n"/>
       <c r="I258" s="7" t="n"/>
       <c r="J258" s="7" t="n"/>
+      <c r="K258" s="7" t="n"/>
+      <c r="L258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -3849,6 +4392,8 @@
       <c r="H259" s="7" t="n"/>
       <c r="I259" s="7" t="n"/>
       <c r="J259" s="7" t="n"/>
+      <c r="K259" s="7" t="n"/>
+      <c r="L259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -3861,6 +4406,8 @@
       <c r="H260" s="7" t="n"/>
       <c r="I260" s="7" t="n"/>
       <c r="J260" s="7" t="n"/>
+      <c r="K260" s="7" t="n"/>
+      <c r="L260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -3873,6 +4420,8 @@
       <c r="H261" s="7" t="n"/>
       <c r="I261" s="7" t="n"/>
       <c r="J261" s="7" t="n"/>
+      <c r="K261" s="7" t="n"/>
+      <c r="L261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -3885,6 +4434,8 @@
       <c r="H262" s="7" t="n"/>
       <c r="I262" s="7" t="n"/>
       <c r="J262" s="7" t="n"/>
+      <c r="K262" s="7" t="n"/>
+      <c r="L262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -3897,6 +4448,8 @@
       <c r="H263" s="7" t="n"/>
       <c r="I263" s="7" t="n"/>
       <c r="J263" s="7" t="n"/>
+      <c r="K263" s="7" t="n"/>
+      <c r="L263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -3909,6 +4462,8 @@
       <c r="H264" s="7" t="n"/>
       <c r="I264" s="7" t="n"/>
       <c r="J264" s="7" t="n"/>
+      <c r="K264" s="7" t="n"/>
+      <c r="L264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -3921,6 +4476,8 @@
       <c r="H265" s="7" t="n"/>
       <c r="I265" s="7" t="n"/>
       <c r="J265" s="7" t="n"/>
+      <c r="K265" s="7" t="n"/>
+      <c r="L265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -3933,6 +4490,8 @@
       <c r="H266" s="7" t="n"/>
       <c r="I266" s="7" t="n"/>
       <c r="J266" s="7" t="n"/>
+      <c r="K266" s="7" t="n"/>
+      <c r="L266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -3945,6 +4504,8 @@
       <c r="H267" s="7" t="n"/>
       <c r="I267" s="7" t="n"/>
       <c r="J267" s="7" t="n"/>
+      <c r="K267" s="7" t="n"/>
+      <c r="L267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -3957,6 +4518,8 @@
       <c r="H268" s="7" t="n"/>
       <c r="I268" s="7" t="n"/>
       <c r="J268" s="7" t="n"/>
+      <c r="K268" s="7" t="n"/>
+      <c r="L268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -3969,6 +4532,8 @@
       <c r="H269" s="7" t="n"/>
       <c r="I269" s="7" t="n"/>
       <c r="J269" s="7" t="n"/>
+      <c r="K269" s="7" t="n"/>
+      <c r="L269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -3981,6 +4546,8 @@
       <c r="H270" s="7" t="n"/>
       <c r="I270" s="7" t="n"/>
       <c r="J270" s="7" t="n"/>
+      <c r="K270" s="7" t="n"/>
+      <c r="L270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -3993,6 +4560,8 @@
       <c r="H271" s="7" t="n"/>
       <c r="I271" s="7" t="n"/>
       <c r="J271" s="7" t="n"/>
+      <c r="K271" s="7" t="n"/>
+      <c r="L271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -4005,6 +4574,8 @@
       <c r="H272" s="7" t="n"/>
       <c r="I272" s="7" t="n"/>
       <c r="J272" s="7" t="n"/>
+      <c r="K272" s="7" t="n"/>
+      <c r="L272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -4017,6 +4588,8 @@
       <c r="H273" s="7" t="n"/>
       <c r="I273" s="7" t="n"/>
       <c r="J273" s="7" t="n"/>
+      <c r="K273" s="7" t="n"/>
+      <c r="L273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -4029,6 +4602,8 @@
       <c r="H274" s="7" t="n"/>
       <c r="I274" s="7" t="n"/>
       <c r="J274" s="7" t="n"/>
+      <c r="K274" s="7" t="n"/>
+      <c r="L274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -4041,6 +4616,8 @@
       <c r="H275" s="7" t="n"/>
       <c r="I275" s="7" t="n"/>
       <c r="J275" s="7" t="n"/>
+      <c r="K275" s="7" t="n"/>
+      <c r="L275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -4053,6 +4630,8 @@
       <c r="H276" s="7" t="n"/>
       <c r="I276" s="7" t="n"/>
       <c r="J276" s="7" t="n"/>
+      <c r="K276" s="7" t="n"/>
+      <c r="L276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -4065,6 +4644,8 @@
       <c r="H277" s="7" t="n"/>
       <c r="I277" s="7" t="n"/>
       <c r="J277" s="7" t="n"/>
+      <c r="K277" s="7" t="n"/>
+      <c r="L277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -4077,6 +4658,8 @@
       <c r="H278" s="7" t="n"/>
       <c r="I278" s="7" t="n"/>
       <c r="J278" s="7" t="n"/>
+      <c r="K278" s="7" t="n"/>
+      <c r="L278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -4089,6 +4672,8 @@
       <c r="H279" s="7" t="n"/>
       <c r="I279" s="7" t="n"/>
       <c r="J279" s="7" t="n"/>
+      <c r="K279" s="7" t="n"/>
+      <c r="L279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -4101,6 +4686,8 @@
       <c r="H280" s="7" t="n"/>
       <c r="I280" s="7" t="n"/>
       <c r="J280" s="7" t="n"/>
+      <c r="K280" s="7" t="n"/>
+      <c r="L280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -4113,6 +4700,8 @@
       <c r="H281" s="7" t="n"/>
       <c r="I281" s="7" t="n"/>
       <c r="J281" s="7" t="n"/>
+      <c r="K281" s="7" t="n"/>
+      <c r="L281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -4125,6 +4714,8 @@
       <c r="H282" s="7" t="n"/>
       <c r="I282" s="7" t="n"/>
       <c r="J282" s="7" t="n"/>
+      <c r="K282" s="7" t="n"/>
+      <c r="L282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -4137,6 +4728,8 @@
       <c r="H283" s="7" t="n"/>
       <c r="I283" s="7" t="n"/>
       <c r="J283" s="7" t="n"/>
+      <c r="K283" s="7" t="n"/>
+      <c r="L283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -4149,6 +4742,8 @@
       <c r="H284" s="7" t="n"/>
       <c r="I284" s="7" t="n"/>
       <c r="J284" s="7" t="n"/>
+      <c r="K284" s="7" t="n"/>
+      <c r="L284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -4161,6 +4756,8 @@
       <c r="H285" s="7" t="n"/>
       <c r="I285" s="7" t="n"/>
       <c r="J285" s="7" t="n"/>
+      <c r="K285" s="7" t="n"/>
+      <c r="L285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -4173,6 +4770,8 @@
       <c r="H286" s="7" t="n"/>
       <c r="I286" s="7" t="n"/>
       <c r="J286" s="7" t="n"/>
+      <c r="K286" s="7" t="n"/>
+      <c r="L286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -4185,6 +4784,8 @@
       <c r="H287" s="7" t="n"/>
       <c r="I287" s="7" t="n"/>
       <c r="J287" s="7" t="n"/>
+      <c r="K287" s="7" t="n"/>
+      <c r="L287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -4197,6 +4798,8 @@
       <c r="H288" s="7" t="n"/>
       <c r="I288" s="7" t="n"/>
       <c r="J288" s="7" t="n"/>
+      <c r="K288" s="7" t="n"/>
+      <c r="L288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -4209,6 +4812,8 @@
       <c r="H289" s="7" t="n"/>
       <c r="I289" s="7" t="n"/>
       <c r="J289" s="7" t="n"/>
+      <c r="K289" s="7" t="n"/>
+      <c r="L289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -4221,6 +4826,8 @@
       <c r="H290" s="7" t="n"/>
       <c r="I290" s="7" t="n"/>
       <c r="J290" s="7" t="n"/>
+      <c r="K290" s="7" t="n"/>
+      <c r="L290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -4233,6 +4840,8 @@
       <c r="H291" s="7" t="n"/>
       <c r="I291" s="7" t="n"/>
       <c r="J291" s="7" t="n"/>
+      <c r="K291" s="7" t="n"/>
+      <c r="L291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -4245,6 +4854,8 @@
       <c r="H292" s="7" t="n"/>
       <c r="I292" s="7" t="n"/>
       <c r="J292" s="7" t="n"/>
+      <c r="K292" s="7" t="n"/>
+      <c r="L292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -4257,6 +4868,8 @@
       <c r="H293" s="7" t="n"/>
       <c r="I293" s="7" t="n"/>
       <c r="J293" s="7" t="n"/>
+      <c r="K293" s="7" t="n"/>
+      <c r="L293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -4269,6 +4882,8 @@
       <c r="H294" s="7" t="n"/>
       <c r="I294" s="7" t="n"/>
       <c r="J294" s="7" t="n"/>
+      <c r="K294" s="7" t="n"/>
+      <c r="L294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -4281,6 +4896,8 @@
       <c r="H295" s="7" t="n"/>
       <c r="I295" s="7" t="n"/>
       <c r="J295" s="7" t="n"/>
+      <c r="K295" s="7" t="n"/>
+      <c r="L295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -4293,6 +4910,8 @@
       <c r="H296" s="7" t="n"/>
       <c r="I296" s="7" t="n"/>
       <c r="J296" s="7" t="n"/>
+      <c r="K296" s="7" t="n"/>
+      <c r="L296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -4305,6 +4924,8 @@
       <c r="H297" s="7" t="n"/>
       <c r="I297" s="7" t="n"/>
       <c r="J297" s="7" t="n"/>
+      <c r="K297" s="7" t="n"/>
+      <c r="L297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -4317,6 +4938,8 @@
       <c r="H298" s="7" t="n"/>
       <c r="I298" s="7" t="n"/>
       <c r="J298" s="7" t="n"/>
+      <c r="K298" s="7" t="n"/>
+      <c r="L298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -4329,6 +4952,8 @@
       <c r="H299" s="7" t="n"/>
       <c r="I299" s="7" t="n"/>
       <c r="J299" s="7" t="n"/>
+      <c r="K299" s="7" t="n"/>
+      <c r="L299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -4341,6 +4966,8 @@
       <c r="H300" s="7" t="n"/>
       <c r="I300" s="7" t="n"/>
       <c r="J300" s="7" t="n"/>
+      <c r="K300" s="7" t="n"/>
+      <c r="L300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -4353,6 +4980,8 @@
       <c r="H301" s="7" t="n"/>
       <c r="I301" s="7" t="n"/>
       <c r="J301" s="7" t="n"/>
+      <c r="K301" s="7" t="n"/>
+      <c r="L301" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
